--- a/PB_Statistics_by_Sector.xlsx
+++ b/PB_Statistics_by_Sector.xlsx
@@ -671,14 +671,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>83.41</v>
+        <v>84.63</v>
       </c>
       <c r="H5" t="n">
         <v>2.27</v>
@@ -687,16 +687,16 @@
         <v>2.89</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="L5" t="n">
         <v>6.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="6">
@@ -718,14 +718,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="G6" t="n">
-        <v>72.09</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>1.83</v>
@@ -737,13 +737,13 @@
         <v>2.76</v>
       </c>
       <c r="K6" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="L6" t="n">
         <v>5.04</v>
       </c>
       <c r="M6" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="7">
@@ -765,14 +765,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="G7" t="n">
-        <v>48.11</v>
+        <v>53.12</v>
       </c>
       <c r="H7" t="n">
         <v>1.4</v>
@@ -781,7 +781,7 @@
         <v>2.18</v>
       </c>
       <c r="J7" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
         <v>3.06</v>
@@ -790,7 +790,7 @@
         <v>4.56</v>
       </c>
       <c r="M7" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="8">
@@ -906,14 +906,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="n">
-        <v>46.86</v>
+        <v>38.92</v>
       </c>
       <c r="H10" t="n">
         <v>1.33</v>
@@ -931,7 +931,7 @@
         <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="11">
@@ -953,14 +953,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="G11" t="n">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="H11" t="n">
         <v>1.96</v>
@@ -978,7 +978,7 @@
         <v>4.82</v>
       </c>
       <c r="M11" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="12">
@@ -1000,14 +1000,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.09</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="H12" t="n">
         <v>1.93</v>
@@ -1016,16 +1016,16 @@
         <v>2.57</v>
       </c>
       <c r="J12" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="K12" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="L12" t="n">
         <v>4.08</v>
       </c>
       <c r="M12" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="13">
@@ -1047,14 +1047,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="G13" t="n">
-        <v>2.91</v>
+        <v>0.7</v>
       </c>
       <c r="H13" t="n">
         <v>1.95</v>
@@ -1066,13 +1066,13 @@
         <v>2.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="L13" t="n">
         <v>4.25</v>
       </c>
       <c r="M13" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="14">
@@ -1141,32 +1141,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.51</v>
+        <v>4.29</v>
       </c>
       <c r="G15" t="n">
-        <v>46.7</v>
+        <v>65.64</v>
       </c>
       <c r="H15" t="n">
         <v>2.06</v>
       </c>
       <c r="I15" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="J15" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
         <v>5.12</v>
       </c>
       <c r="L15" t="n">
-        <v>9.52</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>1152</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="16">
@@ -1188,14 +1188,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>58.57</v>
+        <v>68.95</v>
       </c>
       <c r="H16" t="n">
         <v>2.08</v>
@@ -1213,7 +1213,7 @@
         <v>4.28</v>
       </c>
       <c r="M16" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="17">
@@ -1235,14 +1235,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="G17" t="n">
-        <v>4.64</v>
+        <v>6.16</v>
       </c>
       <c r="H17" t="n">
         <v>2.19</v>
@@ -1251,7 +1251,7 @@
         <v>2.67</v>
       </c>
       <c r="J17" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="K17" t="n">
         <v>3.6</v>
@@ -1260,7 +1260,7 @@
         <v>7.06</v>
       </c>
       <c r="M17" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="18">
@@ -1282,32 +1282,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>4.17</v>
+        <v>14.59</v>
       </c>
       <c r="H18" t="n">
         <v>1.94</v>
       </c>
       <c r="I18" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="J18" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="K18" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="L18" t="n">
         <v>7.29</v>
       </c>
       <c r="M18" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="19">
@@ -1329,14 +1329,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1.99</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77</v>
+        <v>3.9</v>
       </c>
       <c r="H19" t="n">
         <v>1.74</v>
@@ -1345,16 +1345,16 @@
         <v>2.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="K19" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="L19" t="n">
         <v>3.56</v>
       </c>
       <c r="M19" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="20">
@@ -1376,20 +1376,20 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="G20" t="n">
-        <v>4.4</v>
+        <v>8.42</v>
       </c>
       <c r="H20" t="n">
         <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="J20" t="n">
         <v>1.54</v>
@@ -1401,7 +1401,7 @@
         <v>2.02</v>
       </c>
       <c r="M20" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="21">
@@ -1423,14 +1423,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>37.5</v>
+        <v>36.12</v>
       </c>
       <c r="H21" t="n">
         <v>1.42</v>
@@ -1439,16 +1439,16 @@
         <v>2.47</v>
       </c>
       <c r="J21" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L21" t="n">
         <v>5.33</v>
       </c>
       <c r="M21" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="22">
@@ -1470,14 +1470,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1.3</v>
       </c>
       <c r="G22" t="n">
-        <v>53.22</v>
+        <v>52.81</v>
       </c>
       <c r="H22" t="n">
         <v>0.77</v>
@@ -1495,7 +1495,7 @@
         <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="23">
@@ -1517,32 +1517,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G23" t="n">
-        <v>55.27</v>
+        <v>72.7</v>
       </c>
       <c r="H23" t="n">
         <v>2.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="J23" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="K23" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="L23" t="n">
         <v>6.45</v>
       </c>
       <c r="M23" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="24">
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="G24" t="n">
-        <v>15.02</v>
+        <v>19.34</v>
       </c>
       <c r="H24" t="n">
         <v>2.23</v>
       </c>
       <c r="I24" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="K24" t="n">
         <v>4.4</v>
@@ -1589,7 +1589,7 @@
         <v>6.19</v>
       </c>
       <c r="M24" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="25">
@@ -1611,14 +1611,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.26</v>
+        <v>4.76</v>
       </c>
       <c r="G25" t="n">
-        <v>76.89</v>
+        <v>80.97</v>
       </c>
       <c r="H25" t="n">
         <v>1.77</v>
@@ -1630,13 +1630,13 @@
         <v>2.71</v>
       </c>
       <c r="K25" t="n">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="L25" t="n">
         <v>8.68</v>
       </c>
       <c r="M25" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="26">
@@ -1658,14 +1658,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="G26" t="n">
-        <v>30.42</v>
+        <v>40.48</v>
       </c>
       <c r="H26" t="n">
         <v>1.66</v>
@@ -1674,7 +1674,7 @@
         <v>2.07</v>
       </c>
       <c r="J26" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="K26" t="n">
         <v>2.81</v>
@@ -1683,7 +1683,7 @@
         <v>4.73</v>
       </c>
       <c r="M26" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="27">
@@ -1705,14 +1705,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="G27" t="n">
-        <v>49.37</v>
+        <v>59.67</v>
       </c>
       <c r="H27" t="n">
         <v>1.12</v>
@@ -1730,7 +1730,7 @@
         <v>3.59</v>
       </c>
       <c r="M27" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="28">
@@ -1752,14 +1752,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="G28" t="n">
-        <v>22.33</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H28" t="n">
         <v>1.9</v>
@@ -1768,16 +1768,16 @@
         <v>2.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="K28" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L28" t="n">
         <v>3.9</v>
       </c>
       <c r="M28" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="29">
@@ -1799,14 +1799,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G29" t="n">
-        <v>2.12</v>
+        <v>2.89</v>
       </c>
       <c r="H29" t="n">
         <v>1.36</v>
@@ -1815,7 +1815,7 @@
         <v>1.95</v>
       </c>
       <c r="J29" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="K29" t="n">
         <v>2.58</v>
@@ -1824,7 +1824,7 @@
         <v>4.22</v>
       </c>
       <c r="M29" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="30">
@@ -1846,14 +1846,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="G30" t="n">
-        <v>32.08</v>
+        <v>51.09</v>
       </c>
       <c r="H30" t="n">
         <v>1.29</v>
@@ -1871,7 +1871,7 @@
         <v>2.52</v>
       </c>
       <c r="M30" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="31">
@@ -1893,14 +1893,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="G31" t="n">
-        <v>7.15</v>
+        <v>8.66</v>
       </c>
       <c r="H31" t="n">
         <v>1.33</v>
@@ -1909,7 +1909,7 @@
         <v>1.84</v>
       </c>
       <c r="J31" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
@@ -1918,7 +1918,7 @@
         <v>4.17</v>
       </c>
       <c r="M31" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="32">
@@ -1940,14 +1940,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.13</v>
+        <v>3.73</v>
       </c>
       <c r="G32" t="n">
-        <v>77.91</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="H32" t="n">
         <v>1.12</v>
@@ -1956,16 +1956,16 @@
         <v>1.5</v>
       </c>
       <c r="J32" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="K32" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="L32" t="n">
         <v>6.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="33">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="G33" t="n">
-        <v>5.03</v>
+        <v>3.74</v>
       </c>
       <c r="H33" t="n">
         <v>0.58</v>
@@ -2012,7 +2012,7 @@
         <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="34">
@@ -2034,14 +2034,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.26</v>
+        <v>2.59</v>
       </c>
       <c r="G34" t="n">
-        <v>89.39</v>
+        <v>95.94</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2059,7 +2059,7 @@
         <v>3.27</v>
       </c>
       <c r="M34" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="35">
@@ -2081,14 +2081,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="G35" t="n">
-        <v>22.64</v>
+        <v>27.15</v>
       </c>
       <c r="H35" t="n">
         <v>0.77</v>
@@ -2106,7 +2106,7 @@
         <v>1.79</v>
       </c>
       <c r="M35" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="36">
@@ -2128,20 +2128,20 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="G36" t="n">
-        <v>1.57</v>
+        <v>0.16</v>
       </c>
       <c r="H36" t="n">
         <v>0.47</v>
       </c>
       <c r="I36" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="J36" t="n">
         <v>0.65</v>
@@ -2153,7 +2153,7 @@
         <v>0.9</v>
       </c>
       <c r="M36" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="37">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="G39" t="n">
-        <v>28.69</v>
+        <v>35.57</v>
       </c>
       <c r="H39" t="n">
         <v>0.53</v>
       </c>
       <c r="I39" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="J39" t="n">
         <v>0.82</v>
       </c>
       <c r="K39" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="L39" t="n">
         <v>1.08</v>
       </c>
       <c r="M39" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="40">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="G40" t="n">
-        <v>73.73999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="H40" t="n">
         <v>1.96</v>
@@ -2332,16 +2332,16 @@
         <v>2.64</v>
       </c>
       <c r="J40" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="K40" t="n">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="L40" t="n">
         <v>9.029999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="41">
@@ -2363,14 +2363,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.53</v>
+        <v>4.14</v>
       </c>
       <c r="G41" t="n">
-        <v>64.94</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="H41" t="n">
         <v>1.75</v>
@@ -2382,13 +2382,13 @@
         <v>3.14</v>
       </c>
       <c r="K41" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="L41" t="n">
         <v>5.38</v>
       </c>
       <c r="M41" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="42">
@@ -2410,14 +2410,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.83</v>
+        <v>4.08</v>
       </c>
       <c r="G42" t="n">
-        <v>85.3</v>
+        <v>89.08</v>
       </c>
       <c r="H42" t="n">
         <v>2.23</v>
@@ -2426,16 +2426,16 @@
         <v>2.71</v>
       </c>
       <c r="J42" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="K42" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="L42" t="n">
         <v>7.5</v>
       </c>
       <c r="M42" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="43">
@@ -2457,14 +2457,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="G43" t="n">
-        <v>86.40000000000001</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="H43" t="n">
         <v>1.61</v>
@@ -2476,13 +2476,13 @@
         <v>2.04</v>
       </c>
       <c r="K43" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="L43" t="n">
         <v>4.41</v>
       </c>
       <c r="M43" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="44">
@@ -2504,23 +2504,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.27</v>
+        <v>3.13</v>
       </c>
       <c r="G44" t="n">
-        <v>70.2</v>
+        <v>61.08</v>
       </c>
       <c r="H44" t="n">
         <v>1.47</v>
       </c>
       <c r="I44" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="J44" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="K44" t="n">
         <v>3.33</v>
@@ -2529,7 +2529,7 @@
         <v>4.1</v>
       </c>
       <c r="M44" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="45">
@@ -2598,14 +2598,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="G46" t="n">
-        <v>57.78</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="H46" t="n">
         <v>1.31</v>
@@ -2614,7 +2614,7 @@
         <v>1.87</v>
       </c>
       <c r="J46" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="K46" t="n">
         <v>2.28</v>
@@ -2623,7 +2623,7 @@
         <v>2.99</v>
       </c>
       <c r="M46" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="47">
@@ -2645,14 +2645,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="G47" t="n">
-        <v>35.69</v>
+        <v>52.5</v>
       </c>
       <c r="H47" t="n">
         <v>1.01</v>
@@ -2670,7 +2670,7 @@
         <v>2.11</v>
       </c>
       <c r="M47" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="48">
@@ -2739,32 +2739,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="G49" t="n">
-        <v>33.42</v>
+        <v>39.83</v>
       </c>
       <c r="H49" t="n">
         <v>1.68</v>
       </c>
       <c r="I49" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="J49" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="L49" t="n">
-        <v>9.35</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>1164</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="50">
@@ -2786,14 +2786,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="G50" t="n">
-        <v>70.36</v>
+        <v>75.59</v>
       </c>
       <c r="H50" t="n">
         <v>1.79</v>
@@ -2805,13 +2805,13 @@
         <v>2.42</v>
       </c>
       <c r="K50" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="L50" t="n">
         <v>4.03</v>
       </c>
       <c r="M50" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="51">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="G51" t="n">
-        <v>30.66</v>
+        <v>36.27</v>
       </c>
       <c r="H51" t="n">
         <v>1.02</v>
       </c>
       <c r="I51" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J51" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="K51" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="L51" t="n">
         <v>4.86</v>
       </c>
       <c r="M51" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="52">
@@ -2880,14 +2880,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>8.34</v>
+        <v>9.51</v>
       </c>
       <c r="G52" t="n">
-        <v>89.15000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="H52" t="n">
         <v>2.62</v>
@@ -2896,16 +2896,16 @@
         <v>4.15</v>
       </c>
       <c r="J52" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="K52" t="n">
-        <v>6.66</v>
+        <v>6.73</v>
       </c>
       <c r="L52" t="n">
-        <v>9.52</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>1189</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="53">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4.87</v>
+        <v>5.61</v>
       </c>
       <c r="G53" t="n">
-        <v>74.84</v>
+        <v>86.66</v>
       </c>
       <c r="H53" t="n">
         <v>1.72</v>
@@ -2946,13 +2946,13 @@
         <v>3.68</v>
       </c>
       <c r="K53" t="n">
-        <v>4.87</v>
+        <v>4.92</v>
       </c>
       <c r="L53" t="n">
         <v>8.15</v>
       </c>
       <c r="M53" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="54">
@@ -2974,14 +2974,14 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>4.31</v>
+        <v>4.69</v>
       </c>
       <c r="G54" t="n">
-        <v>69.34</v>
+        <v>77.3</v>
       </c>
       <c r="H54" t="n">
         <v>2.14</v>
@@ -2990,16 +2990,16 @@
         <v>2.88</v>
       </c>
       <c r="J54" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="K54" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="L54" t="n">
         <v>5.7</v>
       </c>
       <c r="M54" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="55">
@@ -3021,14 +3021,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>8.199999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>97.89</v>
+        <v>99.92</v>
       </c>
       <c r="H55" t="n">
         <v>1.93</v>
@@ -3037,16 +3037,16 @@
         <v>2.8</v>
       </c>
       <c r="J55" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="K55" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="L55" t="n">
-        <v>9.52</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>1230</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="56">
@@ -3068,14 +3068,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="G56" t="n">
-        <v>78.14</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="H56" t="n">
         <v>1.27</v>
@@ -3093,7 +3093,7 @@
         <v>3.37</v>
       </c>
       <c r="M56" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="57">
@@ -3115,14 +3115,14 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="G57" t="n">
-        <v>60.46</v>
+        <v>53.59</v>
       </c>
       <c r="H57" t="n">
         <v>1.26</v>
@@ -3134,13 +3134,13 @@
         <v>1.54</v>
       </c>
       <c r="K57" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="L57" t="n">
         <v>2.74</v>
       </c>
       <c r="M57" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="58">
@@ -3162,14 +3162,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1.27</v>
       </c>
       <c r="G58" t="n">
-        <v>54.72</v>
+        <v>54.52</v>
       </c>
       <c r="H58" t="n">
         <v>1.04</v>
@@ -3187,7 +3187,7 @@
         <v>2.23</v>
       </c>
       <c r="M58" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="59">
@@ -3350,20 +3350,20 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G62" t="n">
-        <v>21.31</v>
+        <v>20.67</v>
       </c>
       <c r="H62" t="n">
         <v>1.53</v>
       </c>
       <c r="I62" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J62" t="n">
         <v>2.09</v>
@@ -3375,7 +3375,7 @@
         <v>2.75</v>
       </c>
       <c r="M62" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="63">
@@ -3397,20 +3397,20 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="G63" t="n">
-        <v>29.48</v>
+        <v>50.62</v>
       </c>
       <c r="H63" t="n">
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="J63" t="n">
         <v>1.73</v>
@@ -3422,7 +3422,7 @@
         <v>2.42</v>
       </c>
       <c r="M63" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="64">
@@ -3444,14 +3444,14 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G64" t="n">
-        <v>32.78</v>
+        <v>50.7</v>
       </c>
       <c r="H64" t="n">
         <v>1.23</v>
@@ -3469,7 +3469,7 @@
         <v>1.95</v>
       </c>
       <c r="M64" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="65">
@@ -3491,32 +3491,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.51</v>
+        <v>2.91</v>
       </c>
       <c r="G65" t="n">
-        <v>81.76000000000001</v>
+        <v>94.62</v>
       </c>
       <c r="H65" t="n">
         <v>0.93</v>
       </c>
       <c r="I65" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="J65" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="K65" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="L65" t="n">
         <v>3.56</v>
       </c>
       <c r="M65" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="66">
@@ -3679,20 +3679,20 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="G69" t="n">
-        <v>5.74</v>
+        <v>11.31</v>
       </c>
       <c r="H69" t="n">
         <v>1.45</v>
       </c>
       <c r="I69" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J69" t="n">
         <v>2.2</v>
@@ -3704,7 +3704,7 @@
         <v>3.67</v>
       </c>
       <c r="M69" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="70">
@@ -3726,14 +3726,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="G70" t="n">
-        <v>40.09</v>
+        <v>61.23</v>
       </c>
       <c r="H70" t="n">
         <v>1.33</v>
@@ -3742,16 +3742,16 @@
         <v>1.98</v>
       </c>
       <c r="J70" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="K70" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="L70" t="n">
         <v>3.02</v>
       </c>
       <c r="M70" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="71">
@@ -3773,14 +3773,14 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G71" t="n">
-        <v>22.01</v>
+        <v>24.49</v>
       </c>
       <c r="H71" t="n">
         <v>0.92</v>
@@ -3798,7 +3798,7 @@
         <v>2.02</v>
       </c>
       <c r="M71" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="72">
@@ -3820,14 +3820,14 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G72" t="n">
-        <v>43.4</v>
+        <v>44.62</v>
       </c>
       <c r="H72" t="n">
         <v>1.15</v>
@@ -3836,7 +3836,7 @@
         <v>1.53</v>
       </c>
       <c r="J72" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="K72" t="n">
         <v>2.21</v>
@@ -3845,7 +3845,7 @@
         <v>3.61</v>
       </c>
       <c r="M72" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="73">
@@ -3867,14 +3867,14 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="G73" t="n">
-        <v>84.87</v>
+        <v>69.98</v>
       </c>
       <c r="H73" t="n">
         <v>0.47</v>
@@ -3892,7 +3892,7 @@
         <v>0.71</v>
       </c>
       <c r="M73" t="n">
-        <v>866</v>
+        <v>876</v>
       </c>
     </row>
     <row r="74">
@@ -3921,7 +3921,7 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="H74" t="n">
         <v>8.82</v>
@@ -3930,16 +3930,16 @@
         <v>9.23</v>
       </c>
       <c r="J74" t="n">
-        <v>9.359999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K74" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>9.51</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M74" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
@@ -3961,23 +3961,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="G75" t="n">
-        <v>2.67</v>
+        <v>2.26</v>
       </c>
       <c r="H75" t="n">
         <v>2.23</v>
       </c>
       <c r="I75" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="J75" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="K75" t="n">
         <v>4.33</v>
@@ -3986,7 +3986,7 @@
         <v>6.21</v>
       </c>
       <c r="M75" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="76">
@@ -4008,14 +4008,14 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>2.05</v>
       </c>
       <c r="G76" t="n">
-        <v>5.97</v>
+        <v>6.4</v>
       </c>
       <c r="H76" t="n">
         <v>1.9</v>
@@ -4024,7 +4024,7 @@
         <v>2.26</v>
       </c>
       <c r="J76" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="K76" t="n">
         <v>3.55</v>
@@ -4033,7 +4033,7 @@
         <v>7.12</v>
       </c>
       <c r="M76" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="77">
@@ -4058,25 +4058,25 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="H77" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="J77" t="n">
         <v>9.039999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>9.390000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L77" t="n">
-        <v>9.51</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
@@ -4094,32 +4094,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="G78" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
       <c r="H78" t="n">
         <v>3.31</v>
       </c>
       <c r="I78" t="n">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="J78" t="n">
-        <v>6.04</v>
+        <v>5.97</v>
       </c>
       <c r="K78" t="n">
         <v>7.96</v>
       </c>
       <c r="L78" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M78" t="n">
-        <v>1056</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="79">
@@ -4180,14 +4180,14 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="G80" t="n">
-        <v>25.94</v>
+        <v>33.07</v>
       </c>
       <c r="H80" t="n">
         <v>2.09</v>
@@ -4196,16 +4196,16 @@
         <v>3.29</v>
       </c>
       <c r="J80" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="K80" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="L80" t="n">
         <v>6.3</v>
       </c>
       <c r="M80" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="81">
@@ -4223,32 +4223,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>5.76</v>
+        <v>6.92</v>
       </c>
       <c r="G81" t="n">
-        <v>89.52</v>
+        <v>97.58</v>
       </c>
       <c r="H81" t="n">
         <v>2.28</v>
       </c>
       <c r="I81" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="J81" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="K81" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="L81" t="n">
         <v>9.34</v>
       </c>
       <c r="M81" t="n">
-        <v>1269</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="82">
@@ -4309,32 +4309,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="G83" t="n">
-        <v>44.93</v>
+        <v>46.03</v>
       </c>
       <c r="H83" t="n">
         <v>2.05</v>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="J83" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="K83" t="n">
         <v>4.38</v>
       </c>
       <c r="L83" t="n">
-        <v>9.52</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M83" t="n">
-        <v>1084</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="84">
@@ -4352,32 +4352,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="G84" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="H84" t="n">
         <v>2.2</v>
       </c>
       <c r="I84" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="J84" t="n">
         <v>3.6</v>
       </c>
       <c r="K84" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="L84" t="n">
         <v>9.470000000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>1244</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="85">
@@ -4395,32 +4395,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G85" t="n">
-        <v>4.95</v>
+        <v>3.74</v>
       </c>
       <c r="H85" t="n">
         <v>2.26</v>
       </c>
       <c r="I85" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="J85" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="K85" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="L85" t="n">
         <v>5.38</v>
       </c>
       <c r="M85" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="86">
@@ -4438,32 +4438,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="G86" t="n">
-        <v>10.06</v>
+        <v>17.55</v>
       </c>
       <c r="H86" t="n">
         <v>2.09</v>
       </c>
       <c r="I86" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="K86" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="L86" t="n">
         <v>5.78</v>
       </c>
       <c r="M86" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="87">
@@ -4481,14 +4481,14 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="G87" t="n">
-        <v>53.54</v>
+        <v>58.89</v>
       </c>
       <c r="H87" t="n">
         <v>1.65</v>
@@ -4497,7 +4497,7 @@
         <v>2.49</v>
       </c>
       <c r="J87" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="K87" t="n">
         <v>3.94</v>
@@ -4506,7 +4506,7 @@
         <v>5.1</v>
       </c>
       <c r="M87" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="88">
@@ -4524,14 +4524,14 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="G88" t="n">
-        <v>52.44</v>
+        <v>58.66</v>
       </c>
       <c r="H88" t="n">
         <v>1.63</v>
@@ -4549,7 +4549,7 @@
         <v>5.13</v>
       </c>
       <c r="M88" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="89">
@@ -4653,20 +4653,20 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="G91" t="n">
-        <v>8.81</v>
+        <v>6.16</v>
       </c>
       <c r="H91" t="n">
         <v>1.64</v>
       </c>
       <c r="I91" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="J91" t="n">
         <v>2.49</v>
@@ -4678,7 +4678,7 @@
         <v>5.73</v>
       </c>
       <c r="M91" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="92">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="G92" t="n">
-        <v>78.62</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="H92" t="n">
         <v>1.42</v>
@@ -4712,16 +4712,16 @@
         <v>2.09</v>
       </c>
       <c r="J92" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="K92" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="L92" t="n">
         <v>4.35</v>
       </c>
       <c r="M92" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="93">
@@ -4739,32 +4739,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="G93" t="n">
-        <v>70.98999999999999</v>
+        <v>78.63</v>
       </c>
       <c r="H93" t="n">
         <v>1.39</v>
       </c>
       <c r="I93" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="J93" t="n">
         <v>2.3</v>
       </c>
       <c r="K93" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="L93" t="n">
         <v>8.42</v>
       </c>
       <c r="M93" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="94">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="G95" t="n">
-        <v>22.88</v>
+        <v>27.46</v>
       </c>
       <c r="H95" t="n">
         <v>1.52</v>
@@ -4841,7 +4841,7 @@
         <v>1.91</v>
       </c>
       <c r="J95" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="K95" t="n">
         <v>2.4</v>
@@ -4850,7 +4850,7 @@
         <v>3.79</v>
       </c>
       <c r="M95" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="96">
@@ -4868,14 +4868,14 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="G96" t="n">
-        <v>65.48999999999999</v>
+        <v>63.03</v>
       </c>
       <c r="H96" t="n">
         <v>1.19</v>
@@ -4884,7 +4884,7 @@
         <v>1.71</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="K96" t="n">
         <v>2.18</v>
@@ -4893,7 +4893,7 @@
         <v>4.85</v>
       </c>
       <c r="M96" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="97">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="G97" t="n">
-        <v>79.31999999999999</v>
+        <v>88.77</v>
       </c>
       <c r="H97" t="n">
         <v>1.14</v>
@@ -4927,7 +4927,7 @@
         <v>1.73</v>
       </c>
       <c r="J97" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="K97" t="n">
         <v>2.22</v>
@@ -4936,7 +4936,7 @@
         <v>3.19</v>
       </c>
       <c r="M97" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="98">
@@ -4954,23 +4954,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="G98" t="n">
-        <v>66.12</v>
+        <v>66.77</v>
       </c>
       <c r="H98" t="n">
         <v>1.12</v>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J98" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="K98" t="n">
         <v>2.44</v>
@@ -4979,7 +4979,7 @@
         <v>3.14</v>
       </c>
       <c r="M98" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="99">
@@ -4997,14 +4997,14 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G99" t="n">
-        <v>56.68</v>
+        <v>57.57</v>
       </c>
       <c r="H99" t="n">
         <v>1.12</v>
@@ -5013,7 +5013,7 @@
         <v>1.45</v>
       </c>
       <c r="J99" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="K99" t="n">
         <v>1.97</v>
@@ -5022,7 +5022,7 @@
         <v>3.5</v>
       </c>
       <c r="M99" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="100">
@@ -5040,14 +5040,14 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G100" t="n">
-        <v>57.94</v>
+        <v>51.09</v>
       </c>
       <c r="H100" t="n">
         <v>0.99</v>
@@ -5065,7 +5065,7 @@
         <v>1.9</v>
       </c>
       <c r="M100" t="n">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="101">
@@ -5255,14 +5255,14 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="G105" t="n">
-        <v>37.56</v>
+        <v>26.66</v>
       </c>
       <c r="H105" t="n">
         <v>0.47</v>
@@ -5280,7 +5280,7 @@
         <v>1.05</v>
       </c>
       <c r="M105" t="n">
-        <v>1198</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="106">
